--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 44272-2024</t>
+          <t>A 11794-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45573</v>
+        <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 44272-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45573</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4771-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 11794-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46048</v>
+        <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,272 +1666,272 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 60706-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2.4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Blåmossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44599</v>
+        <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2222,35 +2222,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2537,42 +2537,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46119</v>
+        <v>45966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,13 +2606,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2642,39 +2646,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46048</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,42 +2856,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46175</v>
+        <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,20 +2921,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2961,42 +2961,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,19 +3026,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,46 +3062,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51116-2021</t>
+          <t>A 7787-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44461</v>
+        <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7787-2022</t>
+          <t>A 51116-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44608</v>
+        <v>44461</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45366</v>
+        <v>44719</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45095</v>
+        <v>45356</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44757</v>
+        <v>45095</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44785</v>
+        <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44957</v>
+        <v>45455</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44614</v>
+        <v>45797</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44950</v>
+        <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>10.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
         <v>45888</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45852</v>
+        <v>45590</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45908</v>
+        <v>45310</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45716</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45714</v>
+        <v>46037</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45743</v>
+        <v>46037</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45642</v>
+        <v>45908</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45048</v>
+        <v>44950</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45789</v>
+        <v>45726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>45852</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>44547</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5333,14 +5333,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45125</v>
+        <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5413,7 +5413,7 @@
         <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45943</v>
+        <v>45789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45945</v>
+        <v>45259</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45945</v>
+        <v>45714</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45455</v>
+        <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45952</v>
+        <v>45125</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45964</v>
+        <v>44785</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5997,7 +5997,7 @@
         <v>44785</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46119</v>
+        <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44467</v>
+        <v>45945</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45863</v>
+        <v>45945</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45769</v>
+        <v>44950</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46125</v>
+        <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45996</v>
+        <v>44977</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45286</v>
+        <v>44757</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46037</v>
+        <v>45173</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46037</v>
+        <v>45952</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45525</v>
+        <v>45964</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45748</v>
+        <v>46119</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45726</v>
+        <v>46125</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6939,14 +6939,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44602</v>
+        <v>45863</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44547</v>
+        <v>45996</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45401</v>
+        <v>45343</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44582</v>
+        <v>44951</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46161</v>
+        <v>45665</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45134</v>
+        <v>45366</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45173</v>
+        <v>45748</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45215</v>
+        <v>44602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46134</v>
+        <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44719</v>
+        <v>45286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46184</v>
+        <v>46161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44951</v>
+        <v>46134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45209</v>
+        <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
         <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46244</v>
+        <v>45209</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45138</v>
+        <v>44977</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45604</v>
+        <v>46244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45618</v>
+        <v>45642</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44950</v>
+        <v>45618</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>45840</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45840</v>
+        <v>45604</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>44957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45665</v>
+        <v>45215</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45797</v>
+        <v>44582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45644</v>
+        <v>45401</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45590</v>
+        <v>45048</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45716</v>
+        <v>45525</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45310</v>
+        <v>45134</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11794-2025</t>
+          <t>A 44272-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45727</v>
+        <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4771-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 11794-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vanlig groda
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 44272-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45573</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4771-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50295-2024</t>
+          <t>A 4765-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45600</v>
+        <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,272 +1666,272 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53156-2021</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44468</v>
+        <v>45879</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,50 +2109,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 53156-2021 artfynd.xlsx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 53156-2021 karta.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 53156-2021 georefererad karta.tif", "A 53156-2021")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/knärot/A 53156-2021 karta knärot.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 53156-2021 FSC-klagomål.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 53156-2021 FSC-klagomål mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 53156-2021 tillsynsbegäran.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 53156-2021 tillsynsbegäran mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 53156-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46048</v>
+        <v>44468</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2178,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2194,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2206,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2214,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 53156-2021 artfynd.xlsx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 53156-2021 karta.png", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 53156-2021 georefererad karta.tif", "A 53156-2021")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/knärot/A 53156-2021 karta knärot.png", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 53156-2021 FSC-klagomål.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 53156-2021 FSC-klagomål mail.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 53156-2021 tillsynsbegäran.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 53156-2021 tillsynsbegäran mail.docx", "A 53156-2021")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,20 +2287,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45879</v>
+        <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2485,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46119</v>
+        <v>44977</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,7 +2501,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2537,46 +2541,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45966</v>
+        <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2642,46 +2642,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45575</v>
+        <v>45966</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2747,46 +2747,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46175</v>
+        <v>46048</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,42 +2856,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44599</v>
+        <v>46175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2961,42 +2961,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,20 +3026,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,46 +3062,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7787-2022</t>
+          <t>A 51116-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44608</v>
+        <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51116-2021</t>
+          <t>A 7787-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44461</v>
+        <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45366</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44719</v>
+        <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45356</v>
+        <v>44719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45095</v>
+        <v>44757</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44467</v>
+        <v>45743</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45455</v>
+        <v>45267</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45797</v>
+        <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45777</v>
+        <v>44951</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>10.3</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45644</v>
+        <v>44957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45888</v>
+        <v>45125</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4464,7 +4464,7 @@
         <v>45888</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45590</v>
+        <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45310</v>
+        <v>45888</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45716</v>
+        <v>45908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4749,14 +4749,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46037</v>
+        <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46037</v>
+        <v>44950</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45908</v>
+        <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44950</v>
+        <v>46125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45726</v>
+        <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45852</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44547</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5340,7 +5340,7 @@
         <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45630</v>
+        <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45630</v>
+        <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45789</v>
+        <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45259</v>
+        <v>45945</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45714</v>
+        <v>45952</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45943</v>
+        <v>45343</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5844,14 +5844,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45125</v>
+        <v>45964</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44785</v>
+        <v>45642</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44785</v>
+        <v>45748</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>45863</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45945</v>
+        <v>45048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45945</v>
+        <v>45138</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44950</v>
+        <v>45996</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44614</v>
+        <v>45455</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44977</v>
+        <v>44785</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44757</v>
+        <v>45604</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45173</v>
+        <v>46161</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45952</v>
+        <v>44467</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45964</v>
+        <v>45769</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46119</v>
+        <v>46037</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46125</v>
+        <v>46037</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45863</v>
+        <v>46134</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45996</v>
+        <v>45618</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45343</v>
+        <v>45726</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44951</v>
+        <v>45286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45665</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45366</v>
+        <v>45525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45748</v>
+        <v>45209</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7450,14 +7450,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44602</v>
+        <v>46191</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45138</v>
+        <v>44950</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45286</v>
+        <v>45356</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46161</v>
+        <v>44977</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46134</v>
+        <v>46244</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46184</v>
+        <v>44602</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46191</v>
+        <v>44547</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45209</v>
+        <v>45401</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44977</v>
+        <v>44582</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46244</v>
+        <v>46206</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46206</v>
+        <v>45134</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45642</v>
+        <v>45173</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45618</v>
+        <v>45215</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45769</v>
+        <v>44977</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
         <v>45840</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45604</v>
+        <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44957</v>
+        <v>45797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45215</v>
+        <v>45644</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44582</v>
+        <v>45590</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45401</v>
+        <v>45716</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45048</v>
+        <v>45310</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45525</v>
+        <v>45852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45134</v>
+        <v>45714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46048</v>
+        <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,272 +1666,272 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 53156-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45879</v>
+        <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>10.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,46 +2109,50 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 53156-2021 artfynd.xlsx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 53156-2021 karta.png", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 53156-2021 georefererad karta.tif", "A 53156-2021")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/knärot/A 53156-2021 karta knärot.png", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 53156-2021 FSC-klagomål.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 53156-2021 FSC-klagomål mail.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 53156-2021 tillsynsbegäran.docx", "A 53156-2021")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 53156-2021 tillsynsbegäran mail.docx", "A 53156-2021")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53156-2021</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44468</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>10.4</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2190,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2202,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2222,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 53156-2021 artfynd.xlsx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 53156-2021 karta.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 53156-2021 georefererad karta.tif", "A 53156-2021")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/knärot/A 53156-2021 karta knärot.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 53156-2021 FSC-klagomål.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 53156-2021 FSC-klagomål mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 53156-2021 tillsynsbegäran.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 53156-2021 tillsynsbegäran mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44599</v>
+        <v>46048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,42 +2327,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46119</v>
+        <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,50 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2485,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44977</v>
+        <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2501,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2541,42 +2537,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45575</v>
+        <v>46119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,7 +2602,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2642,46 +2638,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45966</v>
+        <v>44599</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2747,46 +2747,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46048</v>
+        <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,35 +2856,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
         <v>46175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>46226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45366</v>
+        <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45095</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44719</v>
+        <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44757</v>
+        <v>44467</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45743</v>
+        <v>45267</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45267</v>
+        <v>45455</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44785</v>
+        <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>10.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44951</v>
+        <v>45644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44957</v>
+        <v>45590</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45125</v>
+        <v>45310</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4464,7 +4464,7 @@
         <v>45888</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10.3</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45888</v>
+        <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45908</v>
+        <v>44950</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4749,14 +4749,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44614</v>
+        <v>45908</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44950</v>
+        <v>44547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46119</v>
+        <v>46037</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46125</v>
+        <v>44785</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45789</v>
+        <v>44785</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>46037</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>44950</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45630</v>
+        <v>45852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5333,14 +5333,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45630</v>
+        <v>44614</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45943</v>
+        <v>45630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45945</v>
+        <v>45630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45945</v>
+        <v>45630</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45952</v>
+        <v>45789</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45343</v>
+        <v>45259</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45964</v>
+        <v>44977</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45642</v>
+        <v>45714</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45748</v>
+        <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45863</v>
+        <v>45943</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45048</v>
+        <v>45743</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45138</v>
+        <v>45945</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45996</v>
+        <v>45945</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45455</v>
+        <v>45173</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44785</v>
+        <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45604</v>
+        <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46161</v>
+        <v>45726</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44467</v>
+        <v>45863</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6720,14 +6720,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45769</v>
+        <v>45125</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46037</v>
+        <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46037</v>
+        <v>45343</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46134</v>
+        <v>44951</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45618</v>
+        <v>45665</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45726</v>
+        <v>45366</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7158,14 +7158,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45286</v>
+        <v>44602</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>45138</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45525</v>
+        <v>45286</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45209</v>
+        <v>46119</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46191</v>
+        <v>46125</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44950</v>
+        <v>44977</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45356</v>
+        <v>45642</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44977</v>
+        <v>45618</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46244</v>
+        <v>45769</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44602</v>
+        <v>45748</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44547</v>
+        <v>45604</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45401</v>
+        <v>44957</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44582</v>
+        <v>45215</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46206</v>
+        <v>44582</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45134</v>
+        <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45173</v>
+        <v>45401</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45215</v>
+        <v>46134</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44977</v>
+        <v>45048</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45840</v>
+        <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45665</v>
+        <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45797</v>
+        <v>45209</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45644</v>
+        <v>46244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45590</v>
+        <v>46206</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45716</v>
+        <v>45840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45310</v>
+        <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45852</v>
+        <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45714</v>
+        <v>45797</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50295-2024</t>
+          <t>A 4765-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45600</v>
+        <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,272 +1666,272 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,20 +2182,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46048</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45879</v>
+        <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2485,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>45879</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,7 +2501,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,46 +2537,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46119</v>
+        <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,7 +2606,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,50 +2642,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44599</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2751,42 +2751,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45575</v>
+        <v>45966</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2852,46 +2852,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46175</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,13 +2921,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2961,42 +2961,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46048</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,46 +3062,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44719</v>
+        <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45095</v>
+        <v>44757</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44467</v>
+        <v>45095</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45267</v>
+        <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45455</v>
+        <v>44957</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45777</v>
+        <v>44614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45644</v>
+        <v>44950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45590</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45310</v>
+        <v>45125</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45888</v>
+        <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         <v>45888</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45716</v>
+        <v>45343</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44950</v>
+        <v>45852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45908</v>
+        <v>45714</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44547</v>
+        <v>45642</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46037</v>
+        <v>46119</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44785</v>
+        <v>45048</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44785</v>
+        <v>45743</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46037</v>
+        <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44950</v>
+        <v>45908</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45852</v>
+        <v>45455</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5333,14 +5333,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44614</v>
+        <v>44785</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45630</v>
+        <v>44467</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45630</v>
+        <v>45748</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45630</v>
+        <v>45769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44977</v>
+        <v>45630</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45714</v>
+        <v>45630</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44757</v>
+        <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45943</v>
+        <v>45286</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45743</v>
+        <v>46161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45945</v>
+        <v>45943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45945</v>
+        <v>45525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45173</v>
+        <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45964</v>
+        <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6574,14 +6574,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45726</v>
+        <v>44602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45863</v>
+        <v>44547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6720,14 +6720,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45125</v>
+        <v>45952</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45996</v>
+        <v>45401</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45343</v>
+        <v>44582</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44951</v>
+        <v>46184</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45665</v>
+        <v>45209</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45366</v>
+        <v>46191</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7158,14 +7158,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44602</v>
+        <v>45964</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45138</v>
+        <v>46244</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45286</v>
+        <v>45863</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46119</v>
+        <v>45134</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46125</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44977</v>
+        <v>45215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>9.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45642</v>
+        <v>46206</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45618</v>
+        <v>44719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45769</v>
+        <v>45996</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45748</v>
+        <v>44951</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45604</v>
+        <v>45840</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44957</v>
+        <v>45138</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45215</v>
+        <v>45604</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44582</v>
+        <v>46037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46161</v>
+        <v>46037</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45401</v>
+        <v>45618</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46134</v>
+        <v>44950</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45048</v>
+        <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46184</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46191</v>
+        <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45209</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46244</v>
+        <v>45665</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46206</v>
+        <v>45797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45840</v>
+        <v>45644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45525</v>
+        <v>45590</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45134</v>
+        <v>45716</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45797</v>
+        <v>45310</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE107"/>
+  <dimension ref="A1:AE108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 60706-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46048</v>
+        <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1678,154 +1678,154 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1849,7 +1849,7 @@
         <v>45600</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44599</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,20 +2287,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46119</v>
+        <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2432,46 +2432,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2485,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45879</v>
+        <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2501,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2541,42 +2537,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45575</v>
+        <v>46175</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,7 +2602,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2646,42 +2642,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46175</v>
+        <v>46119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,7 +2707,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2747,46 +2743,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45966</v>
+        <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2852,46 +2852,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,20 +2921,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2957,46 +2957,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46048</v>
+        <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,13 +3026,13 @@
         </is>
       </c>
       <c r="I24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3066,42 +3066,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>45879</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45366</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44757</v>
+        <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45095</v>
+        <v>44719</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44785</v>
+        <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44957</v>
+        <v>45455</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44614</v>
+        <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44950</v>
+        <v>44547</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45125</v>
+        <v>44785</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45777</v>
+        <v>44950</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.3</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45888</v>
+        <v>44614</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45343</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45852</v>
+        <v>44757</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45714</v>
+        <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45642</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>10.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46119</v>
+        <v>45888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45048</v>
+        <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45743</v>
+        <v>45343</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46125</v>
+        <v>44951</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>45908</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45455</v>
+        <v>45665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44785</v>
+        <v>45366</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44467</v>
+        <v>45748</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45748</v>
+        <v>44602</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45769</v>
+        <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45630</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45630</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45286</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46161</v>
+        <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45525</v>
+        <v>45945</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46134</v>
+        <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45945</v>
+        <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6574,14 +6574,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44602</v>
+        <v>45642</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44547</v>
+        <v>45618</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45952</v>
+        <v>45863</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45401</v>
+        <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44582</v>
+        <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46184</v>
+        <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45209</v>
+        <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46191</v>
+        <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45964</v>
+        <v>45215</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46244</v>
+        <v>46134</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45863</v>
+        <v>44582</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45134</v>
+        <v>45401</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45173</v>
+        <v>46037</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45215</v>
+        <v>46037</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.1</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46206</v>
+        <v>45726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44719</v>
+        <v>45048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7742,14 +7742,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45996</v>
+        <v>45125</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44951</v>
+        <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45840</v>
+        <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45138</v>
+        <v>45209</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45604</v>
+        <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46037</v>
+        <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46037</v>
+        <v>46125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45618</v>
+        <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44950</v>
+        <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>45840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>45134</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45726</v>
+        <v>45797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>46283</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45665</v>
+        <v>45644</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45797</v>
+        <v>45590</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45644</v>
+        <v>45310</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45590</v>
+        <v>45716</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45716</v>
+        <v>45852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45310</v>
+        <v>45714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9116,78 +9116,151 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
+          <t>A 14981-2025</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>45743</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>S 478-2022</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D107" s="1" t="n">
+      <c r="D108" s="1" t="n">
         <v>44587</v>
       </c>
-      <c r="E107" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
+      <c r="E108" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
         <v>1.6</v>
       </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="2" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46048</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45600</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>46175</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>44636</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45879</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44719</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45455</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44547</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44785</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44950</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44614</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>44757</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>45888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45343</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44951</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45908</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45366</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45748</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44602</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45138</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45630</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45630</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45630</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45789</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45259</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45286</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45943</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45945</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45945</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45642</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45618</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45863</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45996</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45215</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>46134</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44582</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45401</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>46037</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>46037</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45125</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45209</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>46125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45134</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45797</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>46283</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45644</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45590</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45310</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45716</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:AE107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46048</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45600</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44599</v>
+        <v>45879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,19 +2287,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,42 +2327,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45966</v>
+        <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46048</v>
+        <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,46 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46175</v>
+        <v>44599</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,20 +2602,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2642,42 +2642,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46119</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2743,50 +2743,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45575</v>
+        <v>46048</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,42 +2852,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44636</v>
+        <v>46119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,7 +2917,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2933,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2945,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2961,35 +2957,39 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
         <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45879</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51116-2021</t>
+          <t>A 7787-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44461</v>
+        <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7787-2022</t>
+          <t>A 3244-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44608</v>
+        <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3244-2022</t>
+          <t>A 54601-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44582</v>
+        <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54601-2021</t>
+          <t>A 9273-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44473</v>
+        <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9273-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44616</v>
+        <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44502</v>
+        <v>44719</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45356</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45095</v>
+        <v>44467</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44719</v>
+        <v>45455</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44467</v>
+        <v>45267</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>7.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45455</v>
+        <v>44950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44950</v>
+        <v>44547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44547</v>
+        <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4318,7 +4318,7 @@
         <v>44785</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44785</v>
+        <v>44950</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,14 +4457,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44950</v>
+        <v>44614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4530,14 +4530,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44614</v>
+        <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>44757</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44757</v>
+        <v>45173</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45173</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>10.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>45743</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.3</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>45888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45343</v>
+        <v>45908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44951</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45908</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45665</v>
+        <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45366</v>
+        <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45748</v>
+        <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44602</v>
+        <v>45259</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45138</v>
+        <v>45748</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45630</v>
+        <v>45343</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45630</v>
+        <v>44951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45630</v>
+        <v>45943</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45630</v>
+        <v>45665</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45789</v>
+        <v>45366</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45259</v>
+        <v>45945</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45286</v>
+        <v>45945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6136,14 +6136,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45943</v>
+        <v>44602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45945</v>
+        <v>46161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44977</v>
+        <v>45138</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45964</v>
+        <v>45286</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45642</v>
+        <v>45863</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45618</v>
+        <v>46134</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45863</v>
+        <v>44977</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45769</v>
+        <v>45996</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46161</v>
+        <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45996</v>
+        <v>45618</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45604</v>
+        <v>45769</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44957</v>
+        <v>46184</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45215</v>
+        <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>9.1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46134</v>
+        <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44582</v>
+        <v>46191</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45401</v>
+        <v>45209</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46037</v>
+        <v>45604</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46037</v>
+        <v>45726</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45726</v>
+        <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45048</v>
+        <v>45215</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>9.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
         <v>45125</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46184</v>
+        <v>44582</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46191</v>
+        <v>45401</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45209</v>
+        <v>46119</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46244</v>
+        <v>46125</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46119</v>
+        <v>45048</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46125</v>
+        <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46206</v>
+        <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45525</v>
+        <v>46283</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45840</v>
+        <v>45525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45134</v>
+        <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45797</v>
+        <v>45134</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46283</v>
+        <v>45797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
         <v>45644</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45590</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45310</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45716</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45714</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9116,27 +9116,27 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107" ht="15" customHeight="1">
+    <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>S 478-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45743</v>
+        <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9188,79 +9188,6 @@
         <v>0</v>
       </c>
       <c r="V107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>S 478-2022</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>44587</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 44272-2024</t>
+          <t>A 11794-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45573</v>
+        <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 44272-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45573</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4771-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 11794-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60706-2023</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45260</v>
+        <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1675,263 +1675,263 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Blåmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,20 +2182,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45879</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45575</v>
+        <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,46 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44599</v>
+        <v>46119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2638,46 +2638,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46175</v>
+        <v>45879</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,13 +2711,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2747,42 +2751,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46048</v>
+        <v>44636</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,7 +2816,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2824,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2836,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2848,46 +2852,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46119</v>
+        <v>45575</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2921,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2953,50 +2957,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46226</v>
+        <v>46175</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,13 +3026,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3066,42 +3066,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44502</v>
+        <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44719</v>
+        <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45356</v>
+        <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45095</v>
+        <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>44467</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45455</v>
+        <v>45366</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45267</v>
+        <v>45769</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44950</v>
+        <v>45095</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44547</v>
+        <v>44757</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4245,7 +4245,7 @@
         <v>44785</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44785</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44950</v>
+        <v>45777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4457,14 +4457,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44614</v>
+        <v>45797</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44977</v>
+        <v>45888</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44757</v>
+        <v>44957</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45173</v>
+        <v>45286</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>45908</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10.3</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45743</v>
+        <v>45525</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45888</v>
+        <v>44602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45888</v>
+        <v>45644</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5041,14 +5041,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45908</v>
+        <v>44614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>44547</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5340,7 +5340,7 @@
         <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45748</v>
+        <v>45590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45343</v>
+        <v>45401</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44951</v>
+        <v>45259</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45943</v>
+        <v>44582</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45665</v>
+        <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45366</v>
+        <v>45943</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5997,7 +5997,7 @@
         <v>45945</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6070,7 +6070,7 @@
         <v>45945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6136,14 +6136,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44602</v>
+        <v>45716</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45952</v>
+        <v>45310</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46161</v>
+        <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45138</v>
+        <v>45964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45964</v>
+        <v>45343</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45286</v>
+        <v>45134</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45863</v>
+        <v>45173</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46134</v>
+        <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44977</v>
+        <v>45863</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45996</v>
+        <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45642</v>
+        <v>45048</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45618</v>
+        <v>44719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45769</v>
+        <v>45996</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46184</v>
+        <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7165,7 +7165,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46037</v>
+        <v>44951</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46191</v>
+        <v>46283</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45209</v>
+        <v>45726</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45604</v>
+        <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7523,14 +7523,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45726</v>
+        <v>45125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44957</v>
+        <v>45138</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45215</v>
+        <v>45604</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7742,14 +7742,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45125</v>
+        <v>45852</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44582</v>
+        <v>45618</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45401</v>
+        <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
         <v>46119</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46125</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45048</v>
+        <v>44950</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46206</v>
+        <v>45356</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45840</v>
+        <v>44977</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46283</v>
+        <v>45743</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45525</v>
+        <v>44977</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46244</v>
+        <v>45748</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45134</v>
+        <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45797</v>
+        <v>46161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45644</v>
+        <v>46134</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45590</v>
+        <v>46184</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45310</v>
+        <v>45209</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45716</v>
+        <v>46191</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45852</v>
+        <v>46206</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45714</v>
+        <v>45840</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE107"/>
+  <dimension ref="A1:AE108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11794-2025</t>
+          <t>A 44272-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45727</v>
+        <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4771-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 11794-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vanlig groda
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 44272-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45573</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4771-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50295-2024</t>
+          <t>A 60706-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45600</v>
+        <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1675,263 +1675,263 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44599</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>45879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45966</v>
+        <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46048</v>
+        <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,46 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46119</v>
+        <v>44599</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,20 +2602,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2638,50 +2638,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45879</v>
+        <v>46048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,13 +2707,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2751,42 +2747,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44636</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2828,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2840,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2852,46 +2848,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45575</v>
+        <v>46119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,7 +2917,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2957,46 +2953,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46175</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,39 +3062,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>46226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45455</v>
+        <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44502</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44785</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44467</v>
+        <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45366</v>
+        <v>45455</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45769</v>
+        <v>44467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45095</v>
+        <v>44950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44757</v>
+        <v>44547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44785</v>
+        <v>44950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>44614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45777</v>
+        <v>44977</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45797</v>
+        <v>44757</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45888</v>
+        <v>44785</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44957</v>
+        <v>44785</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45286</v>
+        <v>45714</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45908</v>
+        <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45525</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44602</v>
+        <v>45743</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45644</v>
+        <v>45888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5041,14 +5041,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44614</v>
+        <v>45888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44547</v>
+        <v>45908</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45590</v>
+        <v>45259</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45401</v>
+        <v>45343</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45259</v>
+        <v>44951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44582</v>
+        <v>45665</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44950</v>
+        <v>45366</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>45943</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5990,14 +5990,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45945</v>
+        <v>44602</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
         <v>45945</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45716</v>
+        <v>45945</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45310</v>
+        <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45952</v>
+        <v>45138</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>45964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45343</v>
+        <v>45286</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45134</v>
+        <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45173</v>
+        <v>45863</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45215</v>
+        <v>44977</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9.1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45863</v>
+        <v>45996</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>45642</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45048</v>
+        <v>45618</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44719</v>
+        <v>46161</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45996</v>
+        <v>45769</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>46037</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44951</v>
+        <v>45604</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46283</v>
+        <v>44957</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
         <v>45726</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46244</v>
+        <v>46134</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7523,14 +7523,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45125</v>
+        <v>45215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>9.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45138</v>
+        <v>44582</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7669,14 +7669,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45604</v>
+        <v>45125</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45852</v>
+        <v>45401</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45618</v>
+        <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45714</v>
+        <v>46191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46119</v>
+        <v>45209</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46125</v>
+        <v>46119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44950</v>
+        <v>46125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45356</v>
+        <v>45048</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44977</v>
+        <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>8.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45743</v>
+        <v>45840</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44977</v>
+        <v>45525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45748</v>
+        <v>46283</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45665</v>
+        <v>45134</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46161</v>
+        <v>46244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46134</v>
+        <v>45797</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46184</v>
+        <v>46289</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45209</v>
+        <v>45644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46191</v>
+        <v>45590</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46206</v>
+        <v>45310</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45840</v>
+        <v>45716</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,118 +9076,191 @@
         </is>
       </c>
       <c r="I106" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>A 35172-2025</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>S 478-2022</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>44587</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
         <v>1.6</v>
       </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>S 478-2022</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>44587</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="2" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60706-2023</t>
+          <t>A 4765-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45260</v>
+        <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1678,260 +1678,260 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Blåmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45879</v>
+        <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,20 +2287,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2327,42 +2327,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45575</v>
+        <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2428,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2537,42 +2537,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44599</v>
+        <v>45966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,19 +2606,19 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2626,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2638,46 +2642,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46048</v>
+        <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,7 +2711,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2747,35 +2751,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2891,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46119</v>
+        <v>45879</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,13 +2921,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2953,50 +2957,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,19 +3026,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,46 +3062,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,20 +3131,20 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44719</v>
+        <v>45366</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>44757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45455</v>
+        <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44467</v>
+        <v>44957</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44950</v>
+        <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44547</v>
+        <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44950</v>
+        <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44614</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44977</v>
+        <v>46037</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44757</v>
+        <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44785</v>
+        <v>45908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4603,14 +4603,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44785</v>
+        <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45714</v>
+        <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45173</v>
+        <v>44950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>45125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.3</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45743</v>
+        <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45888</v>
+        <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45888</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45908</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5194,7 +5194,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45630</v>
+        <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45630</v>
+        <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45789</v>
+        <v>45945</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45259</v>
+        <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45343</v>
+        <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44951</v>
+        <v>45343</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45665</v>
+        <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45366</v>
+        <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45943</v>
+        <v>45964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5990,14 +5990,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44602</v>
+        <v>46125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45945</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45945</v>
+        <v>45048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45952</v>
+        <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45138</v>
+        <v>45310</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45964</v>
+        <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45286</v>
+        <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45748</v>
+        <v>45455</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45863</v>
+        <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44977</v>
+        <v>45748</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 52952-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45996</v>
+        <v>44467</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45642</v>
+        <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45618</v>
+        <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46161</v>
+        <v>45286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45769</v>
+        <v>45852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46037</v>
+        <v>46134</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46037</v>
+        <v>45525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45604</v>
+        <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7304,14 +7304,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44957</v>
+        <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45726</v>
+        <v>44547</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46134</v>
+        <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45215</v>
+        <v>45401</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.1</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44582</v>
+        <v>45209</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7669,14 +7669,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45125</v>
+        <v>44582</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45401</v>
+        <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46184</v>
+        <v>45743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46191</v>
+        <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45209</v>
+        <v>45134</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46119</v>
+        <v>45173</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46125</v>
+        <v>45215</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45048</v>
+        <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46206</v>
+        <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45840</v>
+        <v>44951</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45525</v>
+        <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46283</v>
+        <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45134</v>
+        <v>46289</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46244</v>
+        <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45797</v>
+        <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46289</v>
+        <v>45618</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45644</v>
+        <v>44950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45590</v>
+        <v>45356</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45310</v>
+        <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45716</v>
+        <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9119,7 +9119,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45852</v>
+        <v>45665</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45879</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45366</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44957</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46037</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45945</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45343</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45310</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45455</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45748</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44467</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46134</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44547</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45401</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45209</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44582</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45134</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45173</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45215</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44951</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46289</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45618</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45356</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45665</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>44599</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>46119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45879</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44636</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45366</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44785</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44957</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46037</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45908</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44950</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45945</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>45343</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>46125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45310</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45996</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45455</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45748</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44467</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>45852</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>46134</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44602</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44547</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>46184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45401</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45209</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44582</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45134</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45173</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45215</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45840</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44951</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46289</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45618</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45356</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45665</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:AE107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 44272-2024</t>
+          <t>A 11794-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45573</v>
+        <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 44272-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45573</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4771-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 11794-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46048</v>
+        <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,272 +1666,272 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44468</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46048</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2218,46 +2218,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44599</v>
+        <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,19 +2287,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2323,46 +2323,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44977</v>
+        <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,46 +2428,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46119</v>
+        <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2533,50 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2590,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,13 +2602,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2646,42 +2642,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45575</v>
+        <v>44599</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2751,42 +2751,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46175</v>
+        <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,42 +2856,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45879</v>
+        <v>46175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,13 +2921,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2961,42 +2961,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,20 +3026,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,46 +3062,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3167,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
         <v>44858</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44473</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44616</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44502</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>44719</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45366</v>
+        <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44757</v>
+        <v>45356</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44785</v>
+        <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>10.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44957</v>
+        <v>45797</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45797</v>
+        <v>45455</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>10.3</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46037</v>
+        <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46037</v>
+        <v>45590</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4520,7 +4520,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45908</v>
+        <v>45310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4593,7 +4593,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4603,14 +4603,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44614</v>
+        <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45726</v>
+        <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44950</v>
+        <v>45630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45125</v>
+        <v>45630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45644</v>
+        <v>45630</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>45259</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>44950</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>45943</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45630</v>
+        <v>45945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45259</v>
+        <v>45945</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5396,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45943</v>
+        <v>44547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45945</v>
+        <v>45852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45952</v>
+        <v>44785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45343</v>
+        <v>44785</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46119</v>
+        <v>45714</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45590</v>
+        <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45964</v>
+        <v>44614</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46125</v>
+        <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>45743</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45048</v>
+        <v>44977</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45716</v>
+        <v>46037</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45310</v>
+        <v>46037</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45863</v>
+        <v>44757</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45996</v>
+        <v>45863</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45455</v>
+        <v>45173</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44785</v>
+        <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45748</v>
+        <v>45726</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52952-2021</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6720,14 +6720,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44467</v>
+        <v>45125</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45769</v>
+        <v>45343</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46161</v>
+        <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45286</v>
+        <v>45665</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45852</v>
+        <v>45366</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7085,14 +7085,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46134</v>
+        <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45525</v>
+        <v>45138</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45714</v>
+        <v>45286</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7304,14 +7304,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44602</v>
+        <v>46119</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44547</v>
+        <v>46125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46184</v>
+        <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45401</v>
+        <v>45642</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45209</v>
+        <v>45618</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44582</v>
+        <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46191</v>
+        <v>45748</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45743</v>
+        <v>45604</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46206</v>
+        <v>44957</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45134</v>
+        <v>45215</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>9.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45173</v>
+        <v>46161</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45215</v>
+        <v>44582</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44719</v>
+        <v>45401</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45840</v>
+        <v>46134</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44951</v>
+        <v>45048</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46283</v>
+        <v>46184</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46244</v>
+        <v>46191</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46289</v>
+        <v>45209</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45138</v>
+        <v>46206</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45604</v>
+        <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45618</v>
+        <v>45525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44950</v>
+        <v>45134</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45356</v>
+        <v>46283</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8973,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8987,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44977</v>
+        <v>46244</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44977</v>
+        <v>46289</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9116,27 +9116,27 @@
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
-    <row r="107" ht="15" customHeight="1">
+    <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>S 478-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45665</v>
+        <v>44587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9188,79 +9188,6 @@
         <v>0</v>
       </c>
       <c r="V107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>S 478-2022</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>44587</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE107"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45573</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60706-2023</t>
+          <t>A 4765-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45260</v>
+        <v>46048</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1748,19 +1748,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1784,154 +1784,154 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Blåmossa</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53156-2021</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44468</v>
+        <v>44599</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>10.4</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2109,43 +2109,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 53156-2021 artfynd.xlsx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 53156-2021 karta.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 53156-2021 georefererad karta.tif", "A 53156-2021")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/knärot/A 53156-2021 karta knärot.png", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 53156-2021 FSC-klagomål.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 53156-2021 FSC-klagomål mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 53156-2021 tillsynsbegäran.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 53156-2021 tillsynsbegäran mail.docx", "A 53156-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
@@ -2169,7 +2165,7 @@
         <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2253,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2271,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45966</v>
+        <v>46048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2287,13 +2283,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,39 +2319,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
@@ -2379,7 +2375,7 @@
         <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2463,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46048</v>
+        <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2493,13 @@
         </is>
       </c>
       <c r="I19" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,39 +2529,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
@@ -2589,7 +2585,7 @@
         <v>46119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2681,7 +2677,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2695,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44599</v>
+        <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2711,10 +2707,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2723,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2735,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2751,42 +2747,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45575</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2856,42 +2852,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46175</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2921,13 +2917,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2961,35 +2957,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
@@ -3013,7 +3009,7 @@
         <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3097,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 48215-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3115,10 +3111,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46226</v>
+        <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3131,13 +3127,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3161,52 +3157,20 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
-        <v/>
-      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 48215-2022</t>
+          <t>A 7787-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3220,10 +3184,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44858</v>
+        <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3236,7 +3200,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3279,7 +3243,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7787-2022</t>
+          <t>A 3244-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3293,10 +3257,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44608</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3309,7 +3273,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3352,7 +3316,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3244-2022</t>
+          <t>A 54601-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3366,10 +3330,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44582</v>
+        <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3382,7 +3346,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3425,7 +3389,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54601-2021</t>
+          <t>A 9273-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3439,10 +3403,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44473</v>
+        <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3455,7 +3419,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3498,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9273-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3512,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44616</v>
+        <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3528,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3571,7 +3535,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3585,10 +3549,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44502</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3601,7 +3565,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3644,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3658,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44719</v>
+        <v>45366</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3674,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3717,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3731,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45095</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3747,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3790,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3804,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45356</v>
+        <v>44757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3820,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3863,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3877,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45095</v>
+        <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3893,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3936,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3950,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45777</v>
+        <v>44957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3966,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.3</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4026,7 +3990,7 @@
         <v>45797</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4082,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4096,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45455</v>
+        <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4112,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4155,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4169,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45888</v>
+        <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4185,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4245,7 +4209,7 @@
         <v>45888</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4318,7 +4282,7 @@
         <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4391,7 +4355,7 @@
         <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4464,7 +4428,7 @@
         <v>45590</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4520,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4530,14 +4494,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45310</v>
+        <v>44614</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4550,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4610,7 +4574,7 @@
         <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4666,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4680,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45630</v>
+        <v>45310</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4696,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4739,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4753,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45630</v>
+        <v>46037</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4769,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4812,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4826,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45630</v>
+        <v>46037</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4842,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4885,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4899,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45630</v>
+        <v>44950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4915,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4975,7 +4939,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5031,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5045,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5061,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5104,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5118,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44950</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5134,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5177,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5191,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45943</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5207,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5250,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45945</v>
+        <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5280,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5323,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5337,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45945</v>
+        <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5353,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5396,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5410,10 +5374,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44547</v>
+        <v>45852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5426,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5469,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5483,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45852</v>
+        <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5499,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5542,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5556,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5572,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5615,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5629,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44785</v>
+        <v>45714</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5645,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5688,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5702,10 +5666,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44785</v>
+        <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5718,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5761,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5775,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45714</v>
+        <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5791,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5834,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5848,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44950</v>
+        <v>45343</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5864,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5907,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5917,14 +5881,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44614</v>
+        <v>45743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5937,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5997,7 +5961,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6053,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6067,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45743</v>
+        <v>45726</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6083,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6126,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6140,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44977</v>
+        <v>45642</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6156,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6199,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6213,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46037</v>
+        <v>45048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6229,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6272,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6286,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46037</v>
+        <v>45863</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6302,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6345,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6359,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44757</v>
+        <v>45455</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6375,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6418,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6428,14 +6392,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45863</v>
+        <v>45125</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6448,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6491,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6505,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45173</v>
+        <v>45996</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6521,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6564,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6578,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45996</v>
+        <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6594,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6637,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6651,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45726</v>
+        <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6667,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6710,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6720,14 +6684,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45125</v>
+        <v>46119</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6740,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6783,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6797,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45343</v>
+        <v>46125</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6813,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6856,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6870,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44951</v>
+        <v>45286</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6886,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6929,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6943,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45665</v>
+        <v>45525</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6959,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7002,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7016,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45366</v>
+        <v>45748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7032,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7092,7 +7056,7 @@
         <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7148,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7162,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45138</v>
+        <v>44547</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7178,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7221,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7235,10 +7199,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45286</v>
+        <v>45401</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7294,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7308,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46119</v>
+        <v>44582</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7324,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7367,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7381,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46125</v>
+        <v>46161</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7397,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7440,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7454,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44977</v>
+        <v>45134</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7470,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7513,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7527,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45642</v>
+        <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7543,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7586,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7600,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45618</v>
+        <v>45215</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7616,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7659,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7673,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45769</v>
+        <v>46134</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7689,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7732,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7746,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45748</v>
+        <v>44719</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7762,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7805,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7819,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45604</v>
+        <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7835,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7878,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7892,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44957</v>
+        <v>45209</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7908,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7951,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7965,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45215</v>
+        <v>44951</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7981,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8024,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8038,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46161</v>
+        <v>46191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8054,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8097,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8111,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44582</v>
+        <v>46206</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8127,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8170,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8184,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45401</v>
+        <v>45138</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8243,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8257,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46134</v>
+        <v>45604</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8273,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8316,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8330,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45048</v>
+        <v>45618</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8346,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8389,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8403,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46184</v>
+        <v>44950</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8419,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8462,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8476,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46191</v>
+        <v>45356</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8492,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8535,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8549,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45209</v>
+        <v>44977</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8565,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8608,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8622,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46206</v>
+        <v>45840</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8638,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8681,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8695,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45840</v>
+        <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8711,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8754,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8768,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45525</v>
+        <v>46283</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8784,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8827,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8841,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45134</v>
+        <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8857,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8900,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8914,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46283</v>
+        <v>45665</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8930,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8973,7 +8937,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8987,10 +8951,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46244</v>
+        <v>46289</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9003,7 +8967,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9043,27 +9007,27 @@
       </c>
       <c r="V105" s="2" t="inlineStr"/>
     </row>
-    <row r="106" ht="15" customHeight="1">
+    <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>S 478-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46289</v>
+        <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9076,7 +9040,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9115,79 +9079,6 @@
         <v>0</v>
       </c>
       <c r="V106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>S 478-2022</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>44587</v>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45573</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50295-2024</t>
+          <t>A 60706-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45600</v>
+        <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1675,263 +1675,263 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 4765-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44599</v>
+        <v>44636</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2109,46 +2109,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,20 +2178,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2202,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,46 +2214,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46048</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2319,39 +2319,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46119</v>
+        <v>46048</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2634,50 +2634,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45575</v>
+        <v>46119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,7 +2703,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2743,46 +2739,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46175</v>
+        <v>45575</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2852,42 +2852,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46226</v>
+        <v>46175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2957,42 +2957,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3058,39 +3058,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3244-2022</t>
+          <t>A 54601-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>44473</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54601-2021</t>
+          <t>A 3244-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44473</v>
+        <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45366</v>
+        <v>44719</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45095</v>
+        <v>44614</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44757</v>
+        <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44785</v>
+        <v>45604</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44957</v>
+        <v>44757</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45797</v>
+        <v>45356</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45888</v>
+        <v>44957</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45777</v>
+        <v>45095</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45888</v>
+        <v>45173</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45644</v>
+        <v>45215</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45908</v>
+        <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45590</v>
+        <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44614</v>
+        <v>45525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45716</v>
+        <v>45134</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45310</v>
+        <v>45343</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46037</v>
+        <v>44951</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46037</v>
+        <v>45048</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44950</v>
+        <v>45665</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45789</v>
+        <v>45366</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>44602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>45138</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>45455</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45630</v>
+        <v>45797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45259</v>
+        <v>45286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45852</v>
+        <v>44977</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45943</v>
+        <v>45644</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45945</v>
+        <v>45590</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45714</v>
+        <v>45310</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45945</v>
+        <v>45716</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45952</v>
+        <v>45642</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45343</v>
+        <v>45618</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45743</v>
+        <v>45769</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45964</v>
+        <v>44950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45726</v>
+        <v>45852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45642</v>
+        <v>44547</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45048</v>
+        <v>45714</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45863</v>
+        <v>45259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45455</v>
+        <v>45777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>10.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6392,14 +6392,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45125</v>
+        <v>44785</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45996</v>
+        <v>44785</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44785</v>
+        <v>44950</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45769</v>
+        <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46119</v>
+        <v>45743</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46125</v>
+        <v>45888</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45286</v>
+        <v>45888</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45525</v>
+        <v>45945</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45748</v>
+        <v>45945</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44602</v>
+        <v>45952</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44547</v>
+        <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45401</v>
+        <v>45964</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44582</v>
+        <v>45863</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46161</v>
+        <v>45630</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45134</v>
+        <v>45630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45173</v>
+        <v>45630</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45215</v>
+        <v>45630</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>9.1</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46134</v>
+        <v>45789</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44719</v>
+        <v>45996</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46184</v>
+        <v>46037</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45209</v>
+        <v>46037</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44951</v>
+        <v>45726</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46191</v>
+        <v>45125</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46206</v>
+        <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45138</v>
+        <v>46125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45604</v>
+        <v>45748</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45618</v>
+        <v>46161</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44950</v>
+        <v>46134</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45356</v>
+        <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44977</v>
+        <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45840</v>
+        <v>45209</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44977</v>
+        <v>46206</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46283</v>
+        <v>45840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46244</v>
+        <v>46283</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45665</v>
+        <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>46289</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45573</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60706-2023</t>
+          <t>A 4765-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45260</v>
+        <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
@@ -1678,260 +1678,260 @@
         <v>2</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60706-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Blåmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44636</v>
+        <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,39 +2109,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45879</v>
+        <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2424,46 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,42 +2533,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46048</v>
+        <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2602,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,42 +2642,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46119</v>
+        <v>45879</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,13 +2707,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2739,50 +2743,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45575</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2852,42 +2852,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46175</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2957,42 +2957,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,20 +3022,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3058,39 +3058,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54601-2021</t>
+          <t>A 3244-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44473</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3244-2022</t>
+          <t>A 54601-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44582</v>
+        <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44719</v>
+        <v>45366</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44614</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44977</v>
+        <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45604</v>
+        <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44757</v>
+        <v>44957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45356</v>
+        <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44957</v>
+        <v>46037</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45095</v>
+        <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45173</v>
+        <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45215</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9.1</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>45797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45401</v>
+        <v>45908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45525</v>
+        <v>45726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45134</v>
+        <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45343</v>
+        <v>45789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44951</v>
+        <v>45630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45048</v>
+        <v>45630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45665</v>
+        <v>45630</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45366</v>
+        <v>45125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44602</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45138</v>
+        <v>45259</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45455</v>
+        <v>44950</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45797</v>
+        <v>45644</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45286</v>
+        <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44977</v>
+        <v>45945</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45644</v>
+        <v>45945</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45590</v>
+        <v>45952</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45310</v>
+        <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45716</v>
+        <v>45964</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45642</v>
+        <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45618</v>
+        <v>45343</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45769</v>
+        <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44950</v>
+        <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45852</v>
+        <v>46125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44547</v>
+        <v>45863</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45714</v>
+        <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45259</v>
+        <v>45048</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45777</v>
+        <v>45996</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.3</v>
+        <v>3.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44785</v>
+        <v>45455</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6472,7 +6472,7 @@
         <v>44785</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44950</v>
+        <v>45852</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45943</v>
+        <v>45714</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45743</v>
+        <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45888</v>
+        <v>45769</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45888</v>
+        <v>45743</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45945</v>
+        <v>45286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45945</v>
+        <v>46161</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45952</v>
+        <v>45525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45908</v>
+        <v>46134</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45964</v>
+        <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45863</v>
+        <v>44547</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45630</v>
+        <v>45401</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45630</v>
+        <v>44582</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45630</v>
+        <v>46184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45630</v>
+        <v>45209</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45789</v>
+        <v>46191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45996</v>
+        <v>45134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46037</v>
+        <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46037</v>
+        <v>45215</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45726</v>
+        <v>46206</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45125</v>
+        <v>44719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46119</v>
+        <v>44951</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46125</v>
+        <v>45840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45748</v>
+        <v>45138</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46161</v>
+        <v>45604</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46134</v>
+        <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46184</v>
+        <v>45618</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46191</v>
+        <v>46244</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45209</v>
+        <v>46289</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46206</v>
+        <v>44950</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45840</v>
+        <v>45356</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46283</v>
+        <v>44977</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46244</v>
+        <v>44977</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46289</v>
+        <v>45665</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11794-2025</t>
+          <t>A 44272-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45727</v>
+        <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,151 +1247,151 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 11794-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vanlig groda
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 44272-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45573</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44599</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2202,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,46 +2214,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,42 +2323,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45966</v>
+        <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,42 +2428,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46119</v>
+        <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2497,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2529,50 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45575</v>
+        <v>44599</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,20 +2602,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2642,35 +2642,35 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
         <v>45879</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45366</v>
+        <v>45356</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44785</v>
+        <v>45455</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44957</v>
+        <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>10.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46037</v>
+        <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45777</v>
+        <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
         <v>45797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45908</v>
+        <v>45726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45726</v>
+        <v>44950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44614</v>
+        <v>45630</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4720,7 +4720,7 @@
         <v>45630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4793,7 +4793,7 @@
         <v>45630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45125</v>
+        <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>44547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45259</v>
+        <v>45943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44950</v>
+        <v>45945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45644</v>
+        <v>45945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45943</v>
+        <v>45644</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45945</v>
+        <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45945</v>
+        <v>44785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5516,14 +5516,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45952</v>
+        <v>45125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45590</v>
+        <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5662,14 +5662,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45964</v>
+        <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46119</v>
+        <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45343</v>
+        <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45716</v>
+        <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45310</v>
+        <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46125</v>
+        <v>45310</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45863</v>
+        <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45642</v>
+        <v>45173</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45048</v>
+        <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45996</v>
+        <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45455</v>
+        <v>46119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44785</v>
+        <v>46125</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45852</v>
+        <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45714</v>
+        <v>45343</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45748</v>
+        <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45769</v>
+        <v>45665</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45743</v>
+        <v>45366</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45286</v>
+        <v>45852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6976,14 +6976,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46161</v>
+        <v>44602</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45525</v>
+        <v>45138</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46134</v>
+        <v>45286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44602</v>
+        <v>45748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44547</v>
+        <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45401</v>
+        <v>44977</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44582</v>
+        <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46184</v>
+        <v>46161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45209</v>
+        <v>45618</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46191</v>
+        <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45134</v>
+        <v>45743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45173</v>
+        <v>46134</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45215</v>
+        <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9.1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46206</v>
+        <v>45604</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44719</v>
+        <v>46191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44951</v>
+        <v>45209</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45840</v>
+        <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45138</v>
+        <v>45215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>9.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45604</v>
+        <v>44582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46283</v>
+        <v>45401</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45618</v>
+        <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46244</v>
+        <v>45840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46289</v>
+        <v>45048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44950</v>
+        <v>46283</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45356</v>
+        <v>46289</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44977</v>
+        <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44977</v>
+        <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45665</v>
+        <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44599</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45879</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45356</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45455</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45630</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45644</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45310</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45173</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>46119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46125</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45343</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45665</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45366</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44602</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45138</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44977</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45618</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46134</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45604</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>46191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45209</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45401</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46283</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>46289</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>46048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>44599</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>45879</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44473</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45356</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45095</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45455</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45888</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45908</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44950</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45630</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45630</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45630</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45259</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45943</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45945</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45945</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45644</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44785</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44785</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45590</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45310</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45173</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>46119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46125</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45343</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44951</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45665</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45366</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45852</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44602</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45138</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45748</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44977</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45642</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>46161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45618</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>46134</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45604</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>46191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45209</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45401</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>46206</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>45048</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>46283</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>46289</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>45134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE106"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 11794-2025</t>
+          <t>A 4771-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45727</v>
+        <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1330,13 +1330,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1348,157 +1348,157 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 11794-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vanlig groda
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4771-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46048</v>
+        <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1666,162 +1666,162 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46048</v>
+        <v>44599</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,34 +2073,34 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2113,42 +2113,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2214,46 +2214,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45966</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,42 +2323,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46119</v>
+        <v>45879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2424,50 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45575</v>
+        <v>45966</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,13 +2493,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,46 +2529,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44599</v>
+        <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,10 +2598,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2614,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2626,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2642,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45879</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,13 +2703,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2747,42 +2743,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2792,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46175</v>
+        <v>46226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,13 +2808,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2852,42 +2848,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2897,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,20 +2913,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -2941,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2953,46 +2949,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3002,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,7 +3018,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3034,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3046,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,35 +3058,39 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54601-2021</t>
+          <t>A 9273-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44473</v>
+        <v>44616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9273-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44616</v>
+        <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44502</v>
+        <v>45267</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45366</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45356</v>
+        <v>44757</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44719</v>
+        <v>45095</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45095</v>
+        <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45455</v>
+        <v>44957</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45777</v>
+        <v>46037</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.3</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45888</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45888</v>
+        <v>44614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46037</v>
+        <v>45590</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46037</v>
+        <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45908</v>
+        <v>45310</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45797</v>
+        <v>45888</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45726</v>
+        <v>45777</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.4</v>
+        <v>10.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44950</v>
+        <v>45888</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45630</v>
+        <v>44950</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45630</v>
+        <v>45908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45630</v>
+        <v>45852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45630</v>
+        <v>45714</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45789</v>
+        <v>45343</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45259</v>
+        <v>45743</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44547</v>
+        <v>45726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45943</v>
+        <v>45789</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45945</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45945</v>
+        <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45644</v>
+        <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44785</v>
+        <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44785</v>
+        <v>45259</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5516,14 +5516,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45125</v>
+        <v>45642</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44950</v>
+        <v>45943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5662,14 +5662,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44614</v>
+        <v>45048</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45590</v>
+        <v>45945</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44977</v>
+        <v>45952</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45964</v>
+        <v>45125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45310</v>
+        <v>45455</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44757</v>
+        <v>45964</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45173</v>
+        <v>46119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45716</v>
+        <v>44785</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
         <v>45863</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46119</v>
+        <v>46125</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46125</v>
+        <v>45769</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6545,7 +6545,7 @@
         <v>45996</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45343</v>
+        <v>45286</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44951</v>
+        <v>45525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45665</v>
+        <v>46037</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45366</v>
+        <v>45748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45852</v>
+        <v>44602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6976,14 +6976,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44602</v>
+        <v>44547</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45138</v>
+        <v>45401</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45286</v>
+        <v>44582</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45748</v>
+        <v>46161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45714</v>
+        <v>46134</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44977</v>
+        <v>45134</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45642</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46161</v>
+        <v>45215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.9</v>
+        <v>9.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45618</v>
+        <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45769</v>
+        <v>44719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45743</v>
+        <v>45209</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46134</v>
+        <v>46191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46184</v>
+        <v>44951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45604</v>
+        <v>46206</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46191</v>
+        <v>45138</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45209</v>
+        <v>45604</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44957</v>
+        <v>45840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45215</v>
+        <v>45618</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44582</v>
+        <v>44950</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45401</v>
+        <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46206</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45840</v>
+        <v>46283</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45048</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46289</v>
+        <v>45665</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45525</v>
+        <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8934,27 +8934,27 @@
       </c>
       <c r="V104" s="2" t="inlineStr"/>
     </row>
-    <row r="105" ht="15" customHeight="1">
+    <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>S 478-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45134</v>
+        <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9006,79 +9006,6 @@
         <v>0</v>
       </c>
       <c r="V105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>S 478-2022</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="n">
-        <v>44587</v>
-      </c>
-      <c r="E106" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>46048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>46048</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44599</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,39 +2109,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>45879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2319,46 +2319,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45879</v>
+        <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2424,46 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45966</v>
+        <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2529,46 +2529,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45575</v>
+        <v>46175</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46175</v>
+        <v>44599</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,20 +2703,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2743,35 +2743,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
         <v>46226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44636</v>
+        <v>46119</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2953,42 +2953,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3002,10 +3006,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46119</v>
+        <v>44636</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3018,7 +3022,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3030,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3042,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3058,39 +3062,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45267</v>
+        <v>44719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45366</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44757</v>
+        <v>45356</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>45095</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44785</v>
+        <v>45455</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44957</v>
+        <v>46037</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>46037</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>45777</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44614</v>
+        <v>44950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45590</v>
+        <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45716</v>
+        <v>45888</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45310</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45888</v>
+        <v>44547</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45777</v>
+        <v>45590</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45888</v>
+        <v>45310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44950</v>
+        <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45908</v>
+        <v>45726</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45852</v>
+        <v>44785</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45714</v>
+        <v>44785</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45343</v>
+        <v>45908</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45743</v>
+        <v>44950</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45726</v>
+        <v>44614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45789</v>
+        <v>45125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45630</v>
+        <v>44977</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45630</v>
+        <v>44757</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5304,7 +5304,7 @@
         <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v>45630</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45259</v>
+        <v>45630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45642</v>
+        <v>45630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45943</v>
+        <v>45789</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45048</v>
+        <v>45259</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45945</v>
+        <v>45173</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45945</v>
+        <v>45943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45125</v>
+        <v>45945</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45455</v>
+        <v>45852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45964</v>
+        <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46119</v>
+        <v>45714</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44785</v>
+        <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45863</v>
+        <v>46125</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46125</v>
+        <v>45964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45769</v>
+        <v>45743</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45996</v>
+        <v>45863</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45286</v>
+        <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45525</v>
+        <v>45748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46037</v>
+        <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45748</v>
+        <v>46134</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6903,14 +6903,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44602</v>
+        <v>45343</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44547</v>
+        <v>44951</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45401</v>
+        <v>45665</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44582</v>
+        <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46161</v>
+        <v>44602</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46134</v>
+        <v>46184</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45134</v>
+        <v>46191</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45173</v>
+        <v>45209</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45215</v>
+        <v>45138</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.1</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46184</v>
+        <v>45286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44719</v>
+        <v>44977</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45209</v>
+        <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46191</v>
+        <v>45642</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44951</v>
+        <v>45618</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46206</v>
+        <v>45769</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45138</v>
+        <v>45840</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8078,7 +8078,7 @@
         <v>45604</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45840</v>
+        <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45618</v>
+        <v>45215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>9.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44950</v>
+        <v>44582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>45401</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>46283</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46283</v>
+        <v>45048</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>46289</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46289</v>
+        <v>46244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45665</v>
+        <v>45525</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46244</v>
+        <v>45134</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>45797</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 44272-2024</t>
+          <t>A 11794-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45573</v>
+        <v>45727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 44272-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45573</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 4771-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 11794-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45600</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>46048</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45260</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,46 +2109,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46048</v>
+        <v>45966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="I16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2214,39 +2214,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
         <v>45879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45966</v>
+        <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2428,35 +2428,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
         <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>46175</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44599</v>
+        <v>46048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2743,42 +2743,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31696-2026</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46226</v>
+        <v>44636</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2808,20 +2808,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2832,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2844,46 +2844,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17346-2026</t>
+          <t>A 31696-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46119</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2949,50 +2949,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 31696-2026 artfynd.xlsx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 31696-2026 karta.png", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 31696-2026 georefererad karta.tif", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 31696-2026 FSC-klagomål.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 31696-2026 FSC-klagomål mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 31696-2026 tillsynsbegäran.docx", "A 31696-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 31696-2026 tillsynsbegäran mail.docx", "A 31696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 17346-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3002,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44636</v>
+        <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,7 +3018,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3034,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3046,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3062,35 +3058,39 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 17346-2026 artfynd.xlsx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 17346-2026 karta.png", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 17346-2026 georefererad karta.tif", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 17346-2026 FSC-klagomål.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 17346-2026 FSC-klagomål mail.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 17346-2026 tillsynsbegäran.docx", "A 17346-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 17346-2026 tillsynsbegäran mail.docx", "A 17346-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 17346-2026 prioriterade fågelarter.docx", "A 17346-2026")</f>
         <v/>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44502</v>
+        <v>44785</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44719</v>
+        <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45356</v>
+        <v>45665</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45095</v>
+        <v>45769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45455</v>
+        <v>45366</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46037</v>
+        <v>45095</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46037</v>
+        <v>44757</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44950</v>
+        <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>10.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45644</v>
+        <v>44785</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4209,7 +4209,7 @@
         <v>45888</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45888</v>
+        <v>45797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44547</v>
+        <v>45908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45590</v>
+        <v>45286</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45310</v>
+        <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45716</v>
+        <v>44957</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45726</v>
+        <v>45525</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44785</v>
+        <v>45590</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44785</v>
+        <v>45716</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45908</v>
+        <v>45310</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44950</v>
+        <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44614</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45125</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44977</v>
+        <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44757</v>
+        <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45630</v>
+        <v>45259</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45630</v>
+        <v>44602</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45630</v>
+        <v>44547</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45630</v>
+        <v>45943</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45789</v>
+        <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45259</v>
+        <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45173</v>
+        <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45943</v>
+        <v>45401</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45945</v>
+        <v>44582</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45852</v>
+        <v>44950</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45952</v>
+        <v>45852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45714</v>
+        <v>45964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46119</v>
+        <v>45714</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46125</v>
+        <v>45743</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45964</v>
+        <v>45863</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45743</v>
+        <v>45748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45863</v>
+        <v>45134</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45996</v>
+        <v>45343</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45748</v>
+        <v>45173</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46161</v>
+        <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.9</v>
+        <v>9.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46134</v>
+        <v>45996</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45343</v>
+        <v>45642</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44951</v>
+        <v>46161</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45665</v>
+        <v>45048</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45366</v>
+        <v>44719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44602</v>
+        <v>46134</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46184</v>
+        <v>45455</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46191</v>
+        <v>44951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7418,10 +7418,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45209</v>
+        <v>46037</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45138</v>
+        <v>46037</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45286</v>
+        <v>46184</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44977</v>
+        <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46206</v>
+        <v>45726</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45642</v>
+        <v>46191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7852,14 +7852,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45618</v>
+        <v>45125</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45769</v>
+        <v>45138</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45840</v>
+        <v>45604</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45604</v>
+        <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44957</v>
+        <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45215</v>
+        <v>46119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.1</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44582</v>
+        <v>44950</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45401</v>
+        <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46283</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45048</v>
+        <v>46125</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46289</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32931-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46244</v>
+        <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45525</v>
+        <v>46283</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45134</v>
+        <v>46289</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 32931-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45797</v>
+        <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>44587</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 11794-2025</t>
+          <t>A 44272-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45727</v>
+        <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1247,258 +1247,258 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4771-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 11794-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45727</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vanlig groda
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 44272-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45573</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 44272-2024 artfynd.xlsx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 44272-2024 karta.png", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 44272-2024 georefererad karta.tif", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 44272-2024 FSC-klagomål.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 44272-2024 FSC-klagomål mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 44272-2024 tillsynsbegäran.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 44272-2024 tillsynsbegäran mail.docx", "A 44272-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4771-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50295-2024</t>
+          <t>A 60706-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45600</v>
+        <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1675,263 +1675,263 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 50295-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4765-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 60706-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45260</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 60706-2023 artfynd.xlsx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 60706-2023 karta.png", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 60706-2023 georefererad karta.tif", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 60706-2023 FSC-klagomål.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 60706-2023 FSC-klagomål mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 60706-2023 tillsynsbegäran.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 60706-2023 tillsynsbegäran mail.docx", "A 60706-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 60706-2023 prioriterade fågelarter.docx", "A 60706-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44599</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,46 +2109,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45966</v>
+        <v>45879</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>10.8</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2214,46 +2214,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45879</v>
+        <v>45966</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2319,46 +2319,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44977</v>
+        <v>44599</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,20 +2388,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -2412,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,39 +2424,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
         <v>45575</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46175</v>
+        <v>46048</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46048</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2743,35 +2743,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
         <v>44636</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44785</v>
+        <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44502</v>
+        <v>45267</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45356</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45665</v>
+        <v>45095</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45769</v>
+        <v>44719</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45366</v>
+        <v>45455</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45095</v>
+        <v>44950</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44757</v>
+        <v>44547</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45888</v>
+        <v>44785</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45777</v>
+        <v>44785</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.3</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44785</v>
+        <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45888</v>
+        <v>44614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45797</v>
+        <v>45777</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45908</v>
+        <v>45852</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45286</v>
+        <v>44977</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45644</v>
+        <v>44757</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44957</v>
+        <v>45888</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45525</v>
+        <v>45888</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45590</v>
+        <v>45714</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45716</v>
+        <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45310</v>
+        <v>45743</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45789</v>
+        <v>45908</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57766-2024</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5012,7 +5012,7 @@
         <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57767-2024</t>
+          <t>A 57766-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5085,7 +5085,7 @@
         <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57769-2024</t>
+          <t>A 57767-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5158,7 +5158,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 57769-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5231,7 +5231,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60550-2023</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45259</v>
+        <v>45789</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 60550-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5370,14 +5370,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44602</v>
+        <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44547</v>
+        <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45943</v>
+        <v>45343</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44614</v>
+        <v>44951</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5669,7 +5669,7 @@
         <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,7 +5742,7 @@
         <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45401</v>
+        <v>45665</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44582</v>
+        <v>45366</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45952</v>
+        <v>44602</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44950</v>
+        <v>45952</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45852</v>
+        <v>46119</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>45964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45714</v>
+        <v>45138</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45743</v>
+        <v>46125</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45863</v>
+        <v>45286</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45748</v>
+        <v>45863</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45134</v>
+        <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45343</v>
+        <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45173</v>
+        <v>45642</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45215</v>
+        <v>45618</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45996</v>
+        <v>45769</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45642</v>
+        <v>46037</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46161</v>
+        <v>46037</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45048</v>
+        <v>45604</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44719</v>
+        <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46134</v>
+        <v>45726</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45455</v>
+        <v>44957</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44951</v>
+        <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>9.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7414,14 +7414,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46037</v>
+        <v>45125</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46037</v>
+        <v>44582</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46184</v>
+        <v>45401</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45209</v>
+        <v>46161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45726</v>
+        <v>45048</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46191</v>
+        <v>46134</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7852,14 +7852,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45125</v>
+        <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45138</v>
+        <v>46191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45604</v>
+        <v>45209</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45618</v>
+        <v>46206</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46206</v>
+        <v>45840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46119</v>
+        <v>45525</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44950</v>
+        <v>45134</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>46283</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>45797</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46125</v>
+        <v>46289</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44977</v>
+        <v>45644</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45840</v>
+        <v>45590</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46283</v>
+        <v>45310</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46289</v>
+        <v>45716</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8934,78 +8934,151 @@
       </c>
       <c r="V104" s="2" t="inlineStr"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
+          <t>A 41848-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>S 478-2022</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D105" s="1" t="n">
+      <c r="D106" s="1" t="n">
         <v>44587</v>
       </c>
-      <c r="E105" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
+      <c r="E106" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
         <v>1.6</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="2" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 4771-2026</t>
+          <t>A 11794-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46048</v>
+        <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1330,13 +1330,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1348,157 +1348,157 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 4771-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4771-2026 artfynd.xlsx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4771-2026 karta.png", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4771-2026 georefererad karta.tif", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4771-2026 FSC-klagomål.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4771-2026 FSC-klagomål mail.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4771-2026 tillsynsbegäran.docx", "A 4771-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4771-2026 tillsynsbegäran mail.docx", "A 4771-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 11794-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45727</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 11794-2025 artfynd.xlsx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 11794-2025 karta.png", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 11794-2025 georefererad karta.tif", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 11794-2025 FSC-klagomål.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 11794-2025 FSC-klagomål mail.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 11794-2025 tillsynsbegäran.docx", "A 11794-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 11794-2025 tillsynsbegäran mail.docx", "A 11794-2025")</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4765-2026</t>
+          <t>A 50295-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46048</v>
+        <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1776,162 +1776,162 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 4765-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STENUNGSUND</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4765-2026 artfynd.xlsx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4765-2026 karta.png", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4765-2026 georefererad karta.tif", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4765-2026 FSC-klagomål.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4765-2026 FSC-klagomål mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4765-2026 tillsynsbegäran.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4765-2026 tillsynsbegäran mail.docx", "A 4765-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1415/fåglar/A 4765-2026 prioriterade fågelarter.docx", "A 4765-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50295-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STENUNGSUND</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 50295-2024 artfynd.xlsx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 50295-2024 karta.png", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 50295-2024 georefererad karta.tif", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 50295-2024 FSC-klagomål.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 50295-2024 FSC-klagomål mail.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 50295-2024 tillsynsbegäran.docx", "A 50295-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 50295-2024 tillsynsbegäran mail.docx", "A 50295-2024")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8576-2023</t>
+          <t>A 12075-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>44636</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2113,42 +2113,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bredgentiana</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37539-2025</t>
+          <t>A 6147-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45879</v>
+        <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2178,20 +2178,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2202,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,42 +2218,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54611-2025</t>
+          <t>A 8576-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45966</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2323,42 +2323,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 8576-2023 artfynd.xlsx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 8576-2023 karta.png", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 8576-2023 georefererad karta.tif", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 8576-2023 FSC-klagomål.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 8576-2023 FSC-klagomål mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 8576-2023 tillsynsbegäran.docx", "A 8576-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 8576-2023 tillsynsbegäran mail.docx", "A 8576-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6147-2022</t>
+          <t>A 54611-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44599</v>
+        <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,19 +2388,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2412,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2424,46 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 6147-2022 artfynd.xlsx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 54611-2025 artfynd.xlsx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 6147-2022 karta.png", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 54611-2025 karta.png", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 6147-2022 georefererad karta.tif", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 54611-2025 georefererad karta.tif", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 6147-2022 FSC-klagomål.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 54611-2025 FSC-klagomål.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 6147-2022 FSC-klagomål mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 54611-2025 FSC-klagomål mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 6147-2022 tillsynsbegäran.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 54611-2025 tillsynsbegäran.docx", "A 54611-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 6147-2022 tillsynsbegäran mail.docx", "A 6147-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 54611-2025 tillsynsbegäran mail.docx", "A 54611-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45000-2024</t>
+          <t>A 37539-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45575</v>
+        <v>45879</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2533,42 +2533,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 37539-2025 artfynd.xlsx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 37539-2025 karta.png", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 37539-2025 georefererad karta.tif", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 37539-2025 FSC-klagomål.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 37539-2025 FSC-klagomål mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 37539-2025 tillsynsbegäran.docx", "A 37539-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 37539-2025 tillsynsbegäran mail.docx", "A 37539-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4769-2026</t>
+          <t>A 45000-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46048</v>
+        <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 45000-2024 artfynd.xlsx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 45000-2024 karta.png", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 45000-2024 georefererad karta.tif", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 45000-2024 FSC-klagomål.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 45000-2024 FSC-klagomål mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 45000-2024 tillsynsbegäran.docx", "A 45000-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 45000-2024 tillsynsbegäran mail.docx", "A 45000-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25125-2026</t>
+          <t>A 4769-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46175</v>
+        <v>46048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2743,42 +2743,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 4769-2026 artfynd.xlsx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 4769-2026 karta.png", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 4769-2026 georefererad karta.tif", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 4769-2026 FSC-klagomål.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 4769-2026 FSC-klagomål mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 4769-2026 tillsynsbegäran.docx", "A 4769-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 4769-2026 tillsynsbegäran mail.docx", "A 4769-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12075-2022</t>
+          <t>A 25125-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44636</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2832,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2844,39 +2844,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Bredgentiana</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 12075-2022 artfynd.xlsx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/artfynd/A 25125-2026 artfynd.xlsx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 12075-2022 karta.png", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor/A 25125-2026 karta.png", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 12075-2022 georefererad karta.tif", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/kartor_geotiff/A 25125-2026 georefererad karta.tif", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 12075-2022 FSC-klagomål.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomål/A 25125-2026 FSC-klagomål.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 12075-2022 FSC-klagomål mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/klagomålsmail/A 25125-2026 FSC-klagomål mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 12075-2022 tillsynsbegäran.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsyn/A 25125-2026 tillsynsbegäran.docx", "A 25125-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 12075-2022 tillsynsbegäran mail.docx", "A 12075-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1415/tillsynsmail/A 25125-2026 tillsynsbegäran mail.docx", "A 25125-2026")</f>
         <v/>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9273-2022</t>
+          <t>A 62007-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44616</v>
+        <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62007-2021</t>
+          <t>A 9273-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44502</v>
+        <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2023</t>
+          <t>A 10472-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45267</v>
+        <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8684-2024</t>
+          <t>A 27030-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45356</v>
+        <v>45095</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27030-2023</t>
+          <t>A 62220-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45095</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23070-2022</t>
+          <t>A 30175-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44719</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23762-2024</t>
+          <t>A 33011-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45455</v>
+        <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3570-2023</t>
+          <t>A 64992-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44950</v>
+        <v>45286</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 72944-2021</t>
+          <t>A 4734-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44547</v>
+        <v>44957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33010-2022</t>
+          <t>A 8567-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44785</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33011-2022</t>
+          <t>A 34555-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44785</v>
+        <v>45525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3569-2023</t>
+          <t>A 38996-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44950</v>
+        <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8948-2022</t>
+          <t>A 20974-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44614</v>
+        <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>10.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20974-2025</t>
+          <t>A 38994-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45777</v>
+        <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.3</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35172-2025</t>
+          <t>A 809-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45852</v>
+        <v>45665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8544-2023</t>
+          <t>A 42791-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44977</v>
+        <v>45908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30175-2022</t>
+          <t>A 6699-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44757</v>
+        <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38996-2025</t>
+          <t>A 8948-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45888</v>
+        <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38994-2025</t>
+          <t>A 72944-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45888</v>
+        <v>44547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9282-2025</t>
+          <t>A 15535-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45714</v>
+        <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40950-2023</t>
+          <t>A 3243-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45173</v>
+        <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14981-2025</t>
+          <t>A 3570-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45743</v>
+        <v>44950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42791-2025</t>
+          <t>A 24211-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45908</v>
+        <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57768-2024</t>
+          <t>A 22728-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22728-2025</t>
+          <t>A 57768-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50205-2025</t>
+          <t>A 60832-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45943</v>
+        <v>45644</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6913-2024</t>
+          <t>A 50205-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45343</v>
+        <v>45943</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4578-2023</t>
+          <t>A 48365-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44951</v>
+        <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50538-2025</t>
+          <t>A 50543-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5669,7 +5669,7 @@
         <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50543-2025</t>
+          <t>A 50538-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5742,7 +5742,7 @@
         <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 809-2025</t>
+          <t>A 6913-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45665</v>
+        <v>45343</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10472-2024</t>
+          <t>A 9893-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45366</v>
+        <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6699-2022</t>
+          <t>A 2412-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5954,14 +5954,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44602</v>
+        <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52012-2025</t>
+          <t>A 33950-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45952</v>
+        <v>45134</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17362-2026</t>
+          <t>A 40950-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46119</v>
+        <v>45173</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54247-2025</t>
+          <t>A 51661-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45964</v>
+        <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34253-2023</t>
+          <t>A 52012-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45138</v>
+        <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18016-2026</t>
+          <t>A 60158-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46125</v>
+        <v>45642</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6382,7 +6382,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64992-2023</t>
+          <t>A 19059-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45286</v>
+        <v>45048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6455,7 +6455,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36018-2025</t>
+          <t>A 54247-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45863</v>
+        <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8567-2023</t>
+          <t>A 23070-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>44719</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60687-2025</t>
+          <t>A 23762-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45996</v>
+        <v>45455</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60158-2024</t>
+          <t>A 35172-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45642</v>
+        <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54931-2024</t>
+          <t>A 9282-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45618</v>
+        <v>45714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19302-2025</t>
+          <t>A 36018-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6834,10 +6834,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45769</v>
+        <v>45863</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2472-2026</t>
+          <t>A 4578-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46037</v>
+        <v>44951</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2481-2026</t>
+          <t>A 33010-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46037</v>
+        <v>44785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51367-2024</t>
+          <t>A 14981-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45604</v>
+        <v>45743</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7112,7 +7112,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15726-2025</t>
+          <t>A 19302-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45748</v>
+        <v>45769</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11362-2025</t>
+          <t>A 17362-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45726</v>
+        <v>46119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7258,7 +7258,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4734-2023</t>
+          <t>A 60687-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44957</v>
+        <v>45996</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51661-2023</t>
+          <t>A 18016-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45215</v>
+        <v>46125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>9.1</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7404,7 +7404,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32960-2023</t>
+          <t>A 34253-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7414,14 +7414,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45125</v>
+        <v>45138</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3243-2022</t>
+          <t>A 51367-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44582</v>
+        <v>45604</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15535-2024</t>
+          <t>A 2472-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45401</v>
+        <v>46037</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7623,7 +7623,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23115-2026</t>
+          <t>A 2481-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46161</v>
+        <v>46037</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19059-2023</t>
+          <t>A 54931-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45048</v>
+        <v>45618</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19709-2026</t>
+          <t>A 15726-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46134</v>
+        <v>45748</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26654-2026</t>
+          <t>A 3569-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46184</v>
+        <v>44950</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28665-2026</t>
+          <t>A 8684-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46191</v>
+        <v>45356</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7988,7 +7988,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48895-2023</t>
+          <t>A 8544-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45209</v>
+        <v>44977</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8061,7 +8061,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30170-2026</t>
+          <t>A 11362-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46206</v>
+        <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8134,7 +8134,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 32997-2025</t>
+          <t>A 32960-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8144,14 +8144,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45840</v>
+        <v>45125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34555-2024</t>
+          <t>A 23115-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45525</v>
+        <v>46161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33950-2023</t>
+          <t>A 19709-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45134</v>
+        <v>46134</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38641-2026</t>
+          <t>A 26654-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46283</v>
+        <v>46184</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24211-2025</t>
+          <t>A 48895-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45797</v>
+        <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39682-2026</t>
+          <t>A 28665-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46289</v>
+        <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60832-2024</t>
+          <t>A 30170-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45644</v>
+        <v>46206</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48365-2024</t>
+          <t>A 32997-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45590</v>
+        <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8718,7 +8718,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2412-2024</t>
+          <t>A 38641-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8732,10 +8732,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45310</v>
+        <v>46283</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9893-2025</t>
+          <t>A 39682-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45716</v>
+        <v>46289</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
         <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46303</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>46048</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44636</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45879</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45095</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45286</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>44957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45525</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45888</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45777</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45888</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45665</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45908</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45401</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45797</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45630</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45644</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45943</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45945</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45945</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45343</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45310</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45134</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45173</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45642</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45048</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45964</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44719</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45455</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45863</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44951</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45743</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>45769</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>46119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45996</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>46125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45138</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>45604</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>46037</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46037</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45618</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45748</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>44950</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45356</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>44977</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>45125</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>46161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46134</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>46184</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45209</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>46206</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>45840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>46283</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>46289</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46303</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>

--- a/Översikt STENUNGSUND.xlsx
+++ b/Översikt STENUNGSUND.xlsx
@@ -601,7 +601,7 @@
         <v>45197</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45197</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45667</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45737</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>46141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45573</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45727</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46048</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>45550</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45260</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45600</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>46048</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44636</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44599</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45879</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>46175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>46226</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>46119</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>44858</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44616</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45095</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>44785</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45286</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>44957</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-